--- a/input/試験問題.xlsx
+++ b/input/試験問題.xlsx
@@ -1,21 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10125"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10419"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/NBPlan/TTC/examtools/input/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7004C86A-AC05-984A-8D18-2599216A3C3C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08B91F61-FF09-EE40-BB6C-4D12086D702E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2600" yWindow="1340" windowWidth="32560" windowHeight="25140" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2600" yWindow="780" windowWidth="32560" windowHeight="22600" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1020201" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet2" sheetId="4" r:id="rId2"/>
     <sheet name="2022101" sheetId="2" r:id="rId3"/>
+    <sheet name="Sheet1" sheetId="5" r:id="rId4"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'1020201'!$A$1:$C$556</definedName>
@@ -37,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2336" uniqueCount="646">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2960" uniqueCount="807">
   <si>
     <t>b_exam</t>
   </si>
@@ -2289,6 +2290,490 @@
   </si>
   <si>
     <t>構造体を使うことで得られるメリットとして、誤っているものを選んでください。</t>
+  </si>
+  <si>
+    <t>------</t>
+  </si>
+  <si>
+    <t>Git基本</t>
+  </si>
+  <si>
+    <t>Gitの目的として最も適切なものを1つ選んでください。</t>
+  </si>
+  <si>
+    <t>ファイルを圧縮して容量を減らす</t>
+  </si>
+  <si>
+    <t>ウイルスを自動的に削除する</t>
+  </si>
+  <si>
+    <t>変更履歴を記録し、必要なら過去の状態に戻せるようにする</t>
+  </si>
+  <si>
+    <t>画像を自動で加工する</t>
+  </si>
+  <si>
+    <t>コミットの説明として最も適切なものを1つ選んでください。</t>
+  </si>
+  <si>
+    <t>ファイル名を変更する操作</t>
+  </si>
+  <si>
+    <t>ファイルのその時点の状態を記録として残す操作</t>
+  </si>
+  <si>
+    <t>インターネットに公開する操作</t>
+  </si>
+  <si>
+    <t>フォルダを削除する操作</t>
+  </si>
+  <si>
+    <t>リポジトリの説明として最も適切なものを1つ選んでください。</t>
+  </si>
+  <si>
+    <t>画像ファイルだけを保存する場所</t>
+  </si>
+  <si>
+    <t>Gitをインストールする場所</t>
+  </si>
+  <si>
+    <t>Windowsのごみ箱</t>
+  </si>
+  <si>
+    <t>コミットなどの履歴を保存する保管庫</t>
+  </si>
+  <si>
+    <t>ローカルリポジトリとリモートリポジトリの違いとして最も適切なものを1つ選んでください。</t>
+  </si>
+  <si>
+    <t>ローカルはネット上、リモートは自分のPC内にある</t>
+  </si>
+  <si>
+    <t>ローカルは自分のPC内、リモートはネットワーク上の共有先にある</t>
+  </si>
+  <si>
+    <t>どちらも必ずUSBメモリ上に作る</t>
+  </si>
+  <si>
+    <t>違いはなく、呼び方だけが違う</t>
+  </si>
+  <si>
+    <t>ワークツリーの説明として最も適切なものを1つ選んでください。</t>
+  </si>
+  <si>
+    <t>コミットを保存する場所</t>
+  </si>
+  <si>
+    <t>GitHub上の共有場所</t>
+  </si>
+  <si>
+    <t>変更するファイルを置き、実際に編集する作業場所</t>
+  </si>
+  <si>
+    <t>Gitを削除する場所</t>
+  </si>
+  <si>
+    <t>ステージングエリアの役割として最も適切なものを1つ選んでください。</t>
+  </si>
+  <si>
+    <t>コミットしたい内容を一時的に登録する場所</t>
+  </si>
+  <si>
+    <t>画像を小さくする場所</t>
+  </si>
+  <si>
+    <t>Gitをアンインストールする場所</t>
+  </si>
+  <si>
+    <t>PDFを保存する場所</t>
+  </si>
+  <si>
+    <t>Gitが使える状態か確認するコマンドとして最も適切なものを1つ選んでください。</t>
+  </si>
+  <si>
+    <t>git install</t>
+  </si>
+  <si>
+    <t>git start</t>
+  </si>
+  <si>
+    <t>version git</t>
+  </si>
+  <si>
+    <t>git --version</t>
+  </si>
+  <si>
+    <t># 【問題8】</t>
+  </si>
+  <si>
+    <t>CUI基礎</t>
+  </si>
+  <si>
+    <t>Q008</t>
+  </si>
+  <si>
+    <t>pwd コマンドの説明として正しいものを1つ選んでください。</t>
+  </si>
+  <si>
+    <t>フォルダを作成する</t>
+  </si>
+  <si>
+    <t>現在の作業場所を表示する</t>
+  </si>
+  <si>
+    <t>ファイルを削除する</t>
+  </si>
+  <si>
+    <t>Gitを更新する</t>
+  </si>
+  <si>
+    <t># 【問題9】</t>
+  </si>
+  <si>
+    <t>Q009</t>
+  </si>
+  <si>
+    <t>ls コマンドの役割として正しいものを1つ選んでください。</t>
+  </si>
+  <si>
+    <t>現在のフォルダ内の一覧を表示する</t>
+  </si>
+  <si>
+    <t>フォルダを移動する</t>
+  </si>
+  <si>
+    <t>ファイル名を変更する</t>
+  </si>
+  <si>
+    <t>Gitの履歴を表示する</t>
+  </si>
+  <si>
+    <t># 【問題10】</t>
+  </si>
+  <si>
+    <t>Q010</t>
+  </si>
+  <si>
+    <t>cd コマンドの説明として最も適切なものを1つ選んでください。</t>
+  </si>
+  <si>
+    <t>フォルダを削除する</t>
+  </si>
+  <si>
+    <t>別のフォルダへ移動する</t>
+  </si>
+  <si>
+    <t>ファイル内容を表示する</t>
+  </si>
+  <si>
+    <t># 【問題11】</t>
+  </si>
+  <si>
+    <t>VSCode基礎</t>
+  </si>
+  <si>
+    <t>Q011</t>
+  </si>
+  <si>
+    <t>VSCodeで「Open Folder」を使う理由として最も適切なものを1つ選んでください。</t>
+  </si>
+  <si>
+    <t>フォルダを圧縮するため</t>
+  </si>
+  <si>
+    <t>開いたフォルダ全体を作業場として固定し、作業場所の間違いを減らすため</t>
+  </si>
+  <si>
+    <t>Gitをアンインストールするため</t>
+  </si>
+  <si>
+    <t>画像を編集するため</t>
+  </si>
+  <si>
+    <t># 【問題12】</t>
+  </si>
+  <si>
+    <t>ローカル操作</t>
+  </si>
+  <si>
+    <t>Q012</t>
+  </si>
+  <si>
+    <t>Gitリポジトリを新しく作成するコマンドとして最も適切なものを1つ選んでください。</t>
+  </si>
+  <si>
+    <t>git init</t>
+  </si>
+  <si>
+    <t>git add</t>
+  </si>
+  <si>
+    <t>git log</t>
+  </si>
+  <si>
+    <t>git clone</t>
+  </si>
+  <si>
+    <t># 【問題13】</t>
+  </si>
+  <si>
+    <t>Q013</t>
+  </si>
+  <si>
+    <t>git init を実行したときに作成されるものとして最も適切なものを1つ選んでください。</t>
+  </si>
+  <si>
+    <t>.git フォルダ</t>
+  </si>
+  <si>
+    <t>GitHub フォルダ</t>
+  </si>
+  <si>
+    <t>commit.txt ファイル</t>
+  </si>
+  <si>
+    <t>remote フォルダ</t>
+  </si>
+  <si>
+    <t># 【問題14】</t>
+  </si>
+  <si>
+    <t>Q014</t>
+  </si>
+  <si>
+    <t>Gitで「今の状態」を確認するコマンドとして最も適切なものを1つ選んでください。</t>
+  </si>
+  <si>
+    <t>git status</t>
+  </si>
+  <si>
+    <t># 【問題15】</t>
+  </si>
+  <si>
+    <t>Q015</t>
+  </si>
+  <si>
+    <t>ステージングの説明として最も適切なものを1つ選んでください。</t>
+  </si>
+  <si>
+    <t>GitHubにアップロードすること</t>
+  </si>
+  <si>
+    <t>コミットする内容を選んで登録すること</t>
+  </si>
+  <si>
+    <t>ファイルを削除すること</t>
+  </si>
+  <si>
+    <t>リポジトリを削除すること</t>
+  </si>
+  <si>
+    <t># 【問題16】</t>
+  </si>
+  <si>
+    <t>Q016</t>
+  </si>
+  <si>
+    <t>作業中の変更点を確認するコマンドとして最も適切なものを1つ選んでください。</t>
+  </si>
+  <si>
+    <t>git diff</t>
+  </si>
+  <si>
+    <t># 【問題17】</t>
+  </si>
+  <si>
+    <t>Q017</t>
+  </si>
+  <si>
+    <t>コミット履歴を1行ずつ短く表示するコマンドとして最も適切なものを1つ選んでください。</t>
+  </si>
+  <si>
+    <t>git log --oneline</t>
+  </si>
+  <si>
+    <t>git status --oneline</t>
+  </si>
+  <si>
+    <t>git diff --oneline</t>
+  </si>
+  <si>
+    <t>git init --oneline</t>
+  </si>
+  <si>
+    <t># 【問題18】</t>
+  </si>
+  <si>
+    <t>取り消し</t>
+  </si>
+  <si>
+    <t>Q018</t>
+  </si>
+  <si>
+    <t>まだ add していない作業中の変更を取り消すコマンドとして最も適切なものを1つ選んでください。</t>
+  </si>
+  <si>
+    <t>git log &lt;file&gt;</t>
+  </si>
+  <si>
+    <t>git restore &lt;file&gt;</t>
+  </si>
+  <si>
+    <t>git rm &lt;file&gt;</t>
+  </si>
+  <si>
+    <t>git diff --cached &lt;file&gt;</t>
+  </si>
+  <si>
+    <t># 【問題19】</t>
+  </si>
+  <si>
+    <t>Q019</t>
+  </si>
+  <si>
+    <t>間違って add したファイルをステージから外すコマンドとして最も適切なものを1つ選んでください。</t>
+  </si>
+  <si>
+    <t>git restore --staged &lt;file&gt;</t>
+  </si>
+  <si>
+    <t># 【問題20】</t>
+  </si>
+  <si>
+    <t>除外設定</t>
+  </si>
+  <si>
+    <t>Q020</t>
+  </si>
+  <si>
+    <t>.gitignore の役割として最も適切なものを1つ選んでください。</t>
+  </si>
+  <si>
+    <t>コミットメッセージを自動作成する</t>
+  </si>
+  <si>
+    <t>Gitで管理しないファイルやフォルダを指定する</t>
+  </si>
+  <si>
+    <t>リポジトリを削除する</t>
+  </si>
+  <si>
+    <t>変更点を比較する</t>
+  </si>
+  <si>
+    <t># 【問題21】</t>
+  </si>
+  <si>
+    <t>GitHub連携</t>
+  </si>
+  <si>
+    <t>Q021</t>
+  </si>
+  <si>
+    <t>git clone の説明として最も適切なものを1つ選んでください。</t>
+  </si>
+  <si>
+    <t>ローカルの変更を取り消す操作</t>
+  </si>
+  <si>
+    <t>リモートリポジトリを自分のPCに複製する操作</t>
+  </si>
+  <si>
+    <t>ステージングした内容を取り消す操作</t>
+  </si>
+  <si>
+    <t>ブランチを削除する操作</t>
+  </si>
+  <si>
+    <t># 【問題22】</t>
+  </si>
+  <si>
+    <t>Q022</t>
+  </si>
+  <si>
+    <t>clone後に「クローン元の接続先」を確認するコマンドとして最も適切なものを1つ選んでください。</t>
+  </si>
+  <si>
+    <t>git remote -v</t>
+  </si>
+  <si>
+    <t>git restore --staged</t>
+  </si>
+  <si>
+    <t>git rm -r</t>
+  </si>
+  <si>
+    <t># 【問題23】</t>
+  </si>
+  <si>
+    <t>ブランチ</t>
+  </si>
+  <si>
+    <t>Q023</t>
+  </si>
+  <si>
+    <t>ブランチの説明として最も適切なものを1つ選んでください。</t>
+  </si>
+  <si>
+    <t>変更点だけを表示する機能</t>
+  </si>
+  <si>
+    <t>Gitの履歴を枝分かれさせて並行作業できる仕組み</t>
+  </si>
+  <si>
+    <t>リポジトリを削除する機能</t>
+  </si>
+  <si>
+    <t>ファイルを無視する設定</t>
+  </si>
+  <si>
+    <t># 【問題24】</t>
+  </si>
+  <si>
+    <t>マージ</t>
+  </si>
+  <si>
+    <t>Q024</t>
+  </si>
+  <si>
+    <t>マージの説明として最も適切なものを1つ選んでください。</t>
+  </si>
+  <si>
+    <t>枝分かれしたブランチを統合する操作</t>
+  </si>
+  <si>
+    <t>変更点を表示する操作</t>
+  </si>
+  <si>
+    <t>リモートリポジトリを複製する操作</t>
+  </si>
+  <si>
+    <t># 【問題25】</t>
+  </si>
+  <si>
+    <t>コンフリクト</t>
+  </si>
+  <si>
+    <t>Q025</t>
+  </si>
+  <si>
+    <t>コンフリクトの説明として最も適切なものを1つ選んでください。</t>
+  </si>
+  <si>
+    <t>Gitの機能名で、必ず毎回使う操作</t>
+  </si>
+  <si>
+    <t>GitHubだけで起きるエラー</t>
+  </si>
+  <si>
+    <t>統合時にGitが自動で判断できない状態</t>
+  </si>
+  <si>
+    <t>ファイルが自動的に削除される現象</t>
+  </si>
+  <si>
+    <t>Gitバージョン管理</t>
+    <phoneticPr fontId="1"/>
   </si>
 </sst>
 </file>
@@ -15474,4 +15959,2743 @@
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
   <drawing r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{82F1998B-B48E-9246-BACB-C624E819614E}">
+  <dimension ref="A1:G339"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="20"/>
+  <sheetData>
+    <row r="1" spans="1:7">
+      <c r="A1" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="5"/>
+      <c r="C1" s="16" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="5"/>
+      <c r="G1" s="12"/>
+    </row>
+    <row r="2" spans="1:7" ht="23" customHeight="1">
+      <c r="A2" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="13" t="s">
+        <v>806</v>
+      </c>
+      <c r="G2" s="12"/>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="12"/>
+      <c r="G3" s="12"/>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" t="s">
+        <v>6</v>
+      </c>
+      <c r="G4" s="12"/>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5" t="s">
+        <v>7</v>
+      </c>
+      <c r="G5" s="12"/>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6" t="s">
+        <v>5</v>
+      </c>
+      <c r="B6" t="s">
+        <v>8</v>
+      </c>
+      <c r="G6" s="12"/>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7" t="s">
+        <v>5</v>
+      </c>
+      <c r="B7" t="s">
+        <v>9</v>
+      </c>
+      <c r="G7" s="12"/>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8" t="s">
+        <v>5</v>
+      </c>
+      <c r="B8" t="s">
+        <v>569</v>
+      </c>
+      <c r="G8" s="12"/>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9" t="s">
+        <v>10</v>
+      </c>
+      <c r="B9" s="12"/>
+      <c r="G9" s="12"/>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10" t="s">
+        <v>11</v>
+      </c>
+      <c r="B10" s="10">
+        <v>1020701</v>
+      </c>
+      <c r="C10" s="10"/>
+      <c r="G10" s="12"/>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11" t="s">
+        <v>12</v>
+      </c>
+      <c r="B11" s="10">
+        <v>2026</v>
+      </c>
+      <c r="C11" s="10"/>
+      <c r="G11" s="12"/>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12" t="s">
+        <v>13</v>
+      </c>
+      <c r="B12" s="10" t="s">
+        <v>564</v>
+      </c>
+      <c r="C12" s="10"/>
+      <c r="G12" s="12"/>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13" t="s">
+        <v>14</v>
+      </c>
+      <c r="B13" t="s">
+        <v>565</v>
+      </c>
+      <c r="G13" s="12"/>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14" t="s">
+        <v>15</v>
+      </c>
+      <c r="B14" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="C14" s="10"/>
+      <c r="G14" s="12"/>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="A15" t="s">
+        <v>17</v>
+      </c>
+      <c r="B15" t="s">
+        <v>646</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="A16" t="s">
+        <v>19</v>
+      </c>
+      <c r="B16" t="s">
+        <v>647</v>
+      </c>
+      <c r="C16" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3">
+      <c r="A17" t="s">
+        <v>22</v>
+      </c>
+      <c r="B17" t="s">
+        <v>648</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3">
+      <c r="A18" t="s">
+        <v>24</v>
+      </c>
+      <c r="B18" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3">
+      <c r="A19" t="s">
+        <v>26</v>
+      </c>
+      <c r="B19" t="s">
+        <v>649</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3">
+      <c r="A20" t="s">
+        <v>26</v>
+      </c>
+      <c r="B20" t="s">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3">
+      <c r="A21" t="s">
+        <v>26</v>
+      </c>
+      <c r="B21" t="s">
+        <v>651</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3">
+      <c r="A22" t="s">
+        <v>26</v>
+      </c>
+      <c r="B22" t="s">
+        <v>652</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3">
+      <c r="A23" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3">
+      <c r="A24" t="s">
+        <v>31</v>
+      </c>
+      <c r="B24" t="s">
+        <v>32</v>
+      </c>
+      <c r="C24" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3">
+      <c r="A25" t="s">
+        <v>34</v>
+      </c>
+      <c r="B25">
+        <v>3</v>
+      </c>
+      <c r="C25">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3">
+      <c r="A26" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3">
+      <c r="A27" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3">
+      <c r="A28" t="s">
+        <v>37</v>
+      </c>
+      <c r="B28" t="s">
+        <v>646</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3">
+      <c r="A29" t="s">
+        <v>19</v>
+      </c>
+      <c r="B29" t="s">
+        <v>647</v>
+      </c>
+      <c r="C29" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3">
+      <c r="A30" t="s">
+        <v>22</v>
+      </c>
+      <c r="B30" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3">
+      <c r="A31" t="s">
+        <v>24</v>
+      </c>
+      <c r="B31" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3">
+      <c r="A32" t="s">
+        <v>26</v>
+      </c>
+      <c r="B32" t="s">
+        <v>654</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3">
+      <c r="A33" t="s">
+        <v>26</v>
+      </c>
+      <c r="B33" t="s">
+        <v>655</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3">
+      <c r="A34" t="s">
+        <v>26</v>
+      </c>
+      <c r="B34" t="s">
+        <v>656</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3">
+      <c r="A35" t="s">
+        <v>26</v>
+      </c>
+      <c r="B35" t="s">
+        <v>657</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3">
+      <c r="A36" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3">
+      <c r="A37" t="s">
+        <v>31</v>
+      </c>
+      <c r="B37" t="s">
+        <v>32</v>
+      </c>
+      <c r="C37" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3">
+      <c r="A38" t="s">
+        <v>34</v>
+      </c>
+      <c r="B38">
+        <v>2</v>
+      </c>
+      <c r="C38">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3">
+      <c r="A39" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3">
+      <c r="A40" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3">
+      <c r="A41" t="s">
+        <v>45</v>
+      </c>
+      <c r="B41" t="s">
+        <v>646</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3">
+      <c r="A42" t="s">
+        <v>19</v>
+      </c>
+      <c r="B42" t="s">
+        <v>647</v>
+      </c>
+      <c r="C42" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3">
+      <c r="A43" t="s">
+        <v>22</v>
+      </c>
+      <c r="B43" t="s">
+        <v>658</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3">
+      <c r="A44" t="s">
+        <v>24</v>
+      </c>
+      <c r="B44" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3">
+      <c r="A45" t="s">
+        <v>26</v>
+      </c>
+      <c r="B45" t="s">
+        <v>659</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3">
+      <c r="A46" t="s">
+        <v>26</v>
+      </c>
+      <c r="B46" t="s">
+        <v>660</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3">
+      <c r="A47" t="s">
+        <v>26</v>
+      </c>
+      <c r="B47" t="s">
+        <v>661</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3">
+      <c r="A48" t="s">
+        <v>26</v>
+      </c>
+      <c r="B48" t="s">
+        <v>662</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3">
+      <c r="A49" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3">
+      <c r="A50" t="s">
+        <v>31</v>
+      </c>
+      <c r="B50" t="s">
+        <v>32</v>
+      </c>
+      <c r="C50" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3">
+      <c r="A51" t="s">
+        <v>34</v>
+      </c>
+      <c r="B51">
+        <v>4</v>
+      </c>
+      <c r="C51">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3">
+      <c r="A52" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3">
+      <c r="A53" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3">
+      <c r="A54" t="s">
+        <v>52</v>
+      </c>
+      <c r="B54" t="s">
+        <v>646</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3">
+      <c r="A55" t="s">
+        <v>19</v>
+      </c>
+      <c r="B55" t="s">
+        <v>647</v>
+      </c>
+      <c r="C55" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3">
+      <c r="A56" t="s">
+        <v>22</v>
+      </c>
+      <c r="B56" t="s">
+        <v>663</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3">
+      <c r="A57" t="s">
+        <v>24</v>
+      </c>
+      <c r="B57" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3">
+      <c r="A58" t="s">
+        <v>26</v>
+      </c>
+      <c r="B58" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3">
+      <c r="A59" t="s">
+        <v>26</v>
+      </c>
+      <c r="B59" t="s">
+        <v>665</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3">
+      <c r="A60" t="s">
+        <v>26</v>
+      </c>
+      <c r="B60" t="s">
+        <v>666</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3">
+      <c r="A61" t="s">
+        <v>26</v>
+      </c>
+      <c r="B61" t="s">
+        <v>667</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3">
+      <c r="A62" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3">
+      <c r="A63" t="s">
+        <v>31</v>
+      </c>
+      <c r="B63" t="s">
+        <v>32</v>
+      </c>
+      <c r="C63" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3">
+      <c r="A64" t="s">
+        <v>34</v>
+      </c>
+      <c r="B64">
+        <v>2</v>
+      </c>
+      <c r="C64">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3">
+      <c r="A65" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3">
+      <c r="A66" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3">
+      <c r="A67" t="s">
+        <v>88</v>
+      </c>
+      <c r="B67" t="s">
+        <v>646</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3">
+      <c r="A68" t="s">
+        <v>19</v>
+      </c>
+      <c r="B68" t="s">
+        <v>647</v>
+      </c>
+      <c r="C68" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3">
+      <c r="A69" t="s">
+        <v>22</v>
+      </c>
+      <c r="B69" t="s">
+        <v>668</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3">
+      <c r="A70" t="s">
+        <v>24</v>
+      </c>
+      <c r="B70" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3">
+      <c r="A71" t="s">
+        <v>26</v>
+      </c>
+      <c r="B71" t="s">
+        <v>669</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3">
+      <c r="A72" t="s">
+        <v>26</v>
+      </c>
+      <c r="B72" t="s">
+        <v>670</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3">
+      <c r="A73" t="s">
+        <v>26</v>
+      </c>
+      <c r="B73" t="s">
+        <v>671</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3">
+      <c r="A74" t="s">
+        <v>26</v>
+      </c>
+      <c r="B74" t="s">
+        <v>672</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3">
+      <c r="A75" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3">
+      <c r="A76" t="s">
+        <v>31</v>
+      </c>
+      <c r="B76" t="s">
+        <v>32</v>
+      </c>
+      <c r="C76" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3">
+      <c r="A77" t="s">
+        <v>34</v>
+      </c>
+      <c r="B77">
+        <v>3</v>
+      </c>
+      <c r="C77">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3">
+      <c r="A78" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3">
+      <c r="A79" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3">
+      <c r="A80" t="s">
+        <v>100</v>
+      </c>
+      <c r="B80" t="s">
+        <v>646</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3">
+      <c r="A81" t="s">
+        <v>19</v>
+      </c>
+      <c r="B81" t="s">
+        <v>647</v>
+      </c>
+      <c r="C81" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3">
+      <c r="A82" t="s">
+        <v>22</v>
+      </c>
+      <c r="B82" t="s">
+        <v>673</v>
+      </c>
+    </row>
+    <row r="83" spans="1:3">
+      <c r="A83" t="s">
+        <v>24</v>
+      </c>
+      <c r="B83" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="84" spans="1:3">
+      <c r="A84" t="s">
+        <v>26</v>
+      </c>
+      <c r="B84" t="s">
+        <v>674</v>
+      </c>
+    </row>
+    <row r="85" spans="1:3">
+      <c r="A85" t="s">
+        <v>26</v>
+      </c>
+      <c r="B85" t="s">
+        <v>675</v>
+      </c>
+    </row>
+    <row r="86" spans="1:3">
+      <c r="A86" t="s">
+        <v>26</v>
+      </c>
+      <c r="B86" t="s">
+        <v>676</v>
+      </c>
+    </row>
+    <row r="87" spans="1:3">
+      <c r="A87" t="s">
+        <v>26</v>
+      </c>
+      <c r="B87" t="s">
+        <v>677</v>
+      </c>
+    </row>
+    <row r="88" spans="1:3">
+      <c r="A88" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="89" spans="1:3">
+      <c r="A89" t="s">
+        <v>31</v>
+      </c>
+      <c r="B89" t="s">
+        <v>32</v>
+      </c>
+      <c r="C89" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="90" spans="1:3">
+      <c r="A90" t="s">
+        <v>34</v>
+      </c>
+      <c r="B90">
+        <v>1</v>
+      </c>
+      <c r="C90">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="91" spans="1:3">
+      <c r="A91" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="92" spans="1:3">
+      <c r="A92" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="93" spans="1:3">
+      <c r="A93" t="s">
+        <v>111</v>
+      </c>
+      <c r="B93" t="s">
+        <v>646</v>
+      </c>
+    </row>
+    <row r="94" spans="1:3">
+      <c r="A94" t="s">
+        <v>19</v>
+      </c>
+      <c r="B94" t="s">
+        <v>647</v>
+      </c>
+      <c r="C94" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="95" spans="1:3">
+      <c r="A95" t="s">
+        <v>22</v>
+      </c>
+      <c r="B95" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="96" spans="1:3">
+      <c r="A96" t="s">
+        <v>24</v>
+      </c>
+      <c r="B96" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="97" spans="1:3">
+      <c r="A97" t="s">
+        <v>26</v>
+      </c>
+      <c r="B97" t="s">
+        <v>679</v>
+      </c>
+    </row>
+    <row r="98" spans="1:3">
+      <c r="A98" t="s">
+        <v>26</v>
+      </c>
+      <c r="B98" t="s">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="99" spans="1:3">
+      <c r="A99" t="s">
+        <v>26</v>
+      </c>
+      <c r="B99" t="s">
+        <v>681</v>
+      </c>
+    </row>
+    <row r="100" spans="1:3">
+      <c r="A100" t="s">
+        <v>26</v>
+      </c>
+      <c r="B100" t="s">
+        <v>682</v>
+      </c>
+    </row>
+    <row r="101" spans="1:3">
+      <c r="A101" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="102" spans="1:3">
+      <c r="A102" t="s">
+        <v>31</v>
+      </c>
+      <c r="B102" t="s">
+        <v>32</v>
+      </c>
+      <c r="C102" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="103" spans="1:3">
+      <c r="A103" t="s">
+        <v>34</v>
+      </c>
+      <c r="B103">
+        <v>4</v>
+      </c>
+      <c r="C103">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="104" spans="1:3">
+      <c r="A104" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="105" spans="1:3">
+      <c r="A105" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="106" spans="1:3">
+      <c r="A106" t="s">
+        <v>683</v>
+      </c>
+      <c r="B106" t="s">
+        <v>646</v>
+      </c>
+    </row>
+    <row r="107" spans="1:3">
+      <c r="A107" t="s">
+        <v>19</v>
+      </c>
+      <c r="B107" t="s">
+        <v>684</v>
+      </c>
+      <c r="C107" t="s">
+        <v>685</v>
+      </c>
+    </row>
+    <row r="108" spans="1:3">
+      <c r="A108" t="s">
+        <v>22</v>
+      </c>
+      <c r="B108" t="s">
+        <v>686</v>
+      </c>
+    </row>
+    <row r="109" spans="1:3">
+      <c r="A109" t="s">
+        <v>24</v>
+      </c>
+      <c r="B109" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="110" spans="1:3">
+      <c r="A110" t="s">
+        <v>26</v>
+      </c>
+      <c r="B110" t="s">
+        <v>687</v>
+      </c>
+    </row>
+    <row r="111" spans="1:3">
+      <c r="A111" t="s">
+        <v>26</v>
+      </c>
+      <c r="B111" t="s">
+        <v>688</v>
+      </c>
+    </row>
+    <row r="112" spans="1:3">
+      <c r="A112" t="s">
+        <v>26</v>
+      </c>
+      <c r="B112" t="s">
+        <v>689</v>
+      </c>
+    </row>
+    <row r="113" spans="1:3">
+      <c r="A113" t="s">
+        <v>26</v>
+      </c>
+      <c r="B113" t="s">
+        <v>690</v>
+      </c>
+    </row>
+    <row r="114" spans="1:3">
+      <c r="A114" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="115" spans="1:3">
+      <c r="A115" t="s">
+        <v>31</v>
+      </c>
+      <c r="B115" t="s">
+        <v>32</v>
+      </c>
+      <c r="C115" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="116" spans="1:3">
+      <c r="A116" t="s">
+        <v>34</v>
+      </c>
+      <c r="B116">
+        <v>2</v>
+      </c>
+      <c r="C116">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="117" spans="1:3">
+      <c r="A117" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="118" spans="1:3">
+      <c r="A118" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="119" spans="1:3">
+      <c r="A119" t="s">
+        <v>691</v>
+      </c>
+      <c r="B119" t="s">
+        <v>646</v>
+      </c>
+    </row>
+    <row r="120" spans="1:3">
+      <c r="A120" t="s">
+        <v>19</v>
+      </c>
+      <c r="B120" t="s">
+        <v>684</v>
+      </c>
+      <c r="C120" t="s">
+        <v>692</v>
+      </c>
+    </row>
+    <row r="121" spans="1:3">
+      <c r="A121" t="s">
+        <v>22</v>
+      </c>
+      <c r="B121" t="s">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="122" spans="1:3">
+      <c r="A122" t="s">
+        <v>24</v>
+      </c>
+      <c r="B122" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="123" spans="1:3">
+      <c r="A123" t="s">
+        <v>26</v>
+      </c>
+      <c r="B123" t="s">
+        <v>694</v>
+      </c>
+    </row>
+    <row r="124" spans="1:3">
+      <c r="A124" t="s">
+        <v>26</v>
+      </c>
+      <c r="B124" t="s">
+        <v>695</v>
+      </c>
+    </row>
+    <row r="125" spans="1:3">
+      <c r="A125" t="s">
+        <v>26</v>
+      </c>
+      <c r="B125" t="s">
+        <v>696</v>
+      </c>
+    </row>
+    <row r="126" spans="1:3">
+      <c r="A126" t="s">
+        <v>26</v>
+      </c>
+      <c r="B126" t="s">
+        <v>697</v>
+      </c>
+    </row>
+    <row r="127" spans="1:3">
+      <c r="A127" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="128" spans="1:3">
+      <c r="A128" t="s">
+        <v>31</v>
+      </c>
+      <c r="B128" t="s">
+        <v>32</v>
+      </c>
+      <c r="C128" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="129" spans="1:3">
+      <c r="A129" t="s">
+        <v>34</v>
+      </c>
+      <c r="B129">
+        <v>1</v>
+      </c>
+      <c r="C129">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="130" spans="1:3">
+      <c r="A130" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="131" spans="1:3">
+      <c r="A131" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="132" spans="1:3">
+      <c r="A132" t="s">
+        <v>698</v>
+      </c>
+      <c r="B132" t="s">
+        <v>646</v>
+      </c>
+    </row>
+    <row r="133" spans="1:3">
+      <c r="A133" t="s">
+        <v>19</v>
+      </c>
+      <c r="B133" t="s">
+        <v>684</v>
+      </c>
+      <c r="C133" t="s">
+        <v>699</v>
+      </c>
+    </row>
+    <row r="134" spans="1:3">
+      <c r="A134" t="s">
+        <v>22</v>
+      </c>
+      <c r="B134" t="s">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="135" spans="1:3">
+      <c r="A135" t="s">
+        <v>24</v>
+      </c>
+      <c r="B135" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="136" spans="1:3">
+      <c r="A136" t="s">
+        <v>26</v>
+      </c>
+      <c r="B136" t="s">
+        <v>687</v>
+      </c>
+    </row>
+    <row r="137" spans="1:3">
+      <c r="A137" t="s">
+        <v>26</v>
+      </c>
+      <c r="B137" t="s">
+        <v>701</v>
+      </c>
+    </row>
+    <row r="138" spans="1:3">
+      <c r="A138" t="s">
+        <v>26</v>
+      </c>
+      <c r="B138" t="s">
+        <v>702</v>
+      </c>
+    </row>
+    <row r="139" spans="1:3">
+      <c r="A139" t="s">
+        <v>26</v>
+      </c>
+      <c r="B139" t="s">
+        <v>703</v>
+      </c>
+    </row>
+    <row r="140" spans="1:3">
+      <c r="A140" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="141" spans="1:3">
+      <c r="A141" t="s">
+        <v>31</v>
+      </c>
+      <c r="B141" t="s">
+        <v>32</v>
+      </c>
+      <c r="C141" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="142" spans="1:3">
+      <c r="A142" t="s">
+        <v>34</v>
+      </c>
+      <c r="B142">
+        <v>3</v>
+      </c>
+      <c r="C142">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="143" spans="1:3">
+      <c r="A143" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="144" spans="1:3">
+      <c r="A144" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="145" spans="1:3">
+      <c r="A145" t="s">
+        <v>704</v>
+      </c>
+      <c r="B145" t="s">
+        <v>646</v>
+      </c>
+    </row>
+    <row r="146" spans="1:3">
+      <c r="A146" t="s">
+        <v>19</v>
+      </c>
+      <c r="B146" t="s">
+        <v>705</v>
+      </c>
+      <c r="C146" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="147" spans="1:3">
+      <c r="A147" t="s">
+        <v>22</v>
+      </c>
+      <c r="B147" t="s">
+        <v>707</v>
+      </c>
+    </row>
+    <row r="148" spans="1:3">
+      <c r="A148" t="s">
+        <v>24</v>
+      </c>
+      <c r="B148" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="149" spans="1:3">
+      <c r="A149" t="s">
+        <v>26</v>
+      </c>
+      <c r="B149" t="s">
+        <v>708</v>
+      </c>
+    </row>
+    <row r="150" spans="1:3">
+      <c r="A150" t="s">
+        <v>26</v>
+      </c>
+      <c r="B150" t="s">
+        <v>709</v>
+      </c>
+    </row>
+    <row r="151" spans="1:3">
+      <c r="A151" t="s">
+        <v>26</v>
+      </c>
+      <c r="B151" t="s">
+        <v>710</v>
+      </c>
+    </row>
+    <row r="152" spans="1:3">
+      <c r="A152" t="s">
+        <v>26</v>
+      </c>
+      <c r="B152" t="s">
+        <v>711</v>
+      </c>
+    </row>
+    <row r="153" spans="1:3">
+      <c r="A153" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="154" spans="1:3">
+      <c r="A154" t="s">
+        <v>31</v>
+      </c>
+      <c r="B154" t="s">
+        <v>32</v>
+      </c>
+      <c r="C154" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="155" spans="1:3">
+      <c r="A155" t="s">
+        <v>34</v>
+      </c>
+      <c r="B155">
+        <v>2</v>
+      </c>
+      <c r="C155">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="156" spans="1:3">
+      <c r="A156" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="157" spans="1:3">
+      <c r="A157" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="158" spans="1:3">
+      <c r="A158" t="s">
+        <v>712</v>
+      </c>
+      <c r="B158" t="s">
+        <v>646</v>
+      </c>
+    </row>
+    <row r="159" spans="1:3">
+      <c r="A159" t="s">
+        <v>19</v>
+      </c>
+      <c r="B159" t="s">
+        <v>713</v>
+      </c>
+      <c r="C159" t="s">
+        <v>714</v>
+      </c>
+    </row>
+    <row r="160" spans="1:3">
+      <c r="A160" t="s">
+        <v>22</v>
+      </c>
+      <c r="B160" t="s">
+        <v>715</v>
+      </c>
+    </row>
+    <row r="161" spans="1:3">
+      <c r="A161" t="s">
+        <v>24</v>
+      </c>
+      <c r="B161" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="162" spans="1:3">
+      <c r="A162" t="s">
+        <v>26</v>
+      </c>
+      <c r="B162" t="s">
+        <v>716</v>
+      </c>
+    </row>
+    <row r="163" spans="1:3">
+      <c r="A163" t="s">
+        <v>26</v>
+      </c>
+      <c r="B163" t="s">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="164" spans="1:3">
+      <c r="A164" t="s">
+        <v>26</v>
+      </c>
+      <c r="B164" t="s">
+        <v>718</v>
+      </c>
+    </row>
+    <row r="165" spans="1:3">
+      <c r="A165" t="s">
+        <v>26</v>
+      </c>
+      <c r="B165" t="s">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="166" spans="1:3">
+      <c r="A166" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="167" spans="1:3">
+      <c r="A167" t="s">
+        <v>31</v>
+      </c>
+      <c r="B167" t="s">
+        <v>32</v>
+      </c>
+      <c r="C167" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="168" spans="1:3">
+      <c r="A168" t="s">
+        <v>34</v>
+      </c>
+      <c r="B168">
+        <v>1</v>
+      </c>
+      <c r="C168">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="169" spans="1:3">
+      <c r="A169" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="170" spans="1:3">
+      <c r="A170" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="171" spans="1:3">
+      <c r="A171" t="s">
+        <v>720</v>
+      </c>
+      <c r="B171" t="s">
+        <v>646</v>
+      </c>
+    </row>
+    <row r="172" spans="1:3">
+      <c r="A172" t="s">
+        <v>19</v>
+      </c>
+      <c r="B172" t="s">
+        <v>713</v>
+      </c>
+      <c r="C172" t="s">
+        <v>721</v>
+      </c>
+    </row>
+    <row r="173" spans="1:3">
+      <c r="A173" t="s">
+        <v>22</v>
+      </c>
+      <c r="B173" t="s">
+        <v>722</v>
+      </c>
+    </row>
+    <row r="174" spans="1:3">
+      <c r="A174" t="s">
+        <v>24</v>
+      </c>
+      <c r="B174" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="175" spans="1:3">
+      <c r="A175" t="s">
+        <v>26</v>
+      </c>
+      <c r="B175" t="s">
+        <v>723</v>
+      </c>
+    </row>
+    <row r="176" spans="1:3">
+      <c r="A176" t="s">
+        <v>26</v>
+      </c>
+      <c r="B176" t="s">
+        <v>724</v>
+      </c>
+    </row>
+    <row r="177" spans="1:3">
+      <c r="A177" t="s">
+        <v>26</v>
+      </c>
+      <c r="B177" t="s">
+        <v>725</v>
+      </c>
+    </row>
+    <row r="178" spans="1:3">
+      <c r="A178" t="s">
+        <v>26</v>
+      </c>
+      <c r="B178" t="s">
+        <v>726</v>
+      </c>
+    </row>
+    <row r="179" spans="1:3">
+      <c r="A179" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="180" spans="1:3">
+      <c r="A180" t="s">
+        <v>31</v>
+      </c>
+      <c r="B180" t="s">
+        <v>32</v>
+      </c>
+      <c r="C180" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="181" spans="1:3">
+      <c r="A181" t="s">
+        <v>34</v>
+      </c>
+      <c r="B181">
+        <v>1</v>
+      </c>
+      <c r="C181">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="182" spans="1:3">
+      <c r="A182" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="183" spans="1:3">
+      <c r="A183" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="184" spans="1:3">
+      <c r="A184" t="s">
+        <v>727</v>
+      </c>
+      <c r="B184" t="s">
+        <v>646</v>
+      </c>
+    </row>
+    <row r="185" spans="1:3">
+      <c r="A185" t="s">
+        <v>19</v>
+      </c>
+      <c r="B185" t="s">
+        <v>713</v>
+      </c>
+      <c r="C185" t="s">
+        <v>728</v>
+      </c>
+    </row>
+    <row r="186" spans="1:3">
+      <c r="A186" t="s">
+        <v>22</v>
+      </c>
+      <c r="B186" t="s">
+        <v>729</v>
+      </c>
+    </row>
+    <row r="187" spans="1:3">
+      <c r="A187" t="s">
+        <v>24</v>
+      </c>
+      <c r="B187" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="188" spans="1:3">
+      <c r="A188" t="s">
+        <v>26</v>
+      </c>
+      <c r="B188" t="s">
+        <v>718</v>
+      </c>
+    </row>
+    <row r="189" spans="1:3">
+      <c r="A189" t="s">
+        <v>26</v>
+      </c>
+      <c r="B189" t="s">
+        <v>730</v>
+      </c>
+    </row>
+    <row r="190" spans="1:3">
+      <c r="A190" t="s">
+        <v>26</v>
+      </c>
+      <c r="B190" t="s">
+        <v>716</v>
+      </c>
+    </row>
+    <row r="191" spans="1:3">
+      <c r="A191" t="s">
+        <v>26</v>
+      </c>
+      <c r="B191" t="s">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="192" spans="1:3">
+      <c r="A192" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="193" spans="1:3">
+      <c r="A193" t="s">
+        <v>31</v>
+      </c>
+      <c r="B193" t="s">
+        <v>32</v>
+      </c>
+      <c r="C193" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="194" spans="1:3">
+      <c r="A194" t="s">
+        <v>34</v>
+      </c>
+      <c r="B194">
+        <v>2</v>
+      </c>
+      <c r="C194">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="195" spans="1:3">
+      <c r="A195" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="196" spans="1:3">
+      <c r="A196" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="197" spans="1:3">
+      <c r="A197" t="s">
+        <v>731</v>
+      </c>
+      <c r="B197" t="s">
+        <v>646</v>
+      </c>
+    </row>
+    <row r="198" spans="1:3">
+      <c r="A198" t="s">
+        <v>19</v>
+      </c>
+      <c r="B198" t="s">
+        <v>713</v>
+      </c>
+      <c r="C198" t="s">
+        <v>732</v>
+      </c>
+    </row>
+    <row r="199" spans="1:3">
+      <c r="A199" t="s">
+        <v>22</v>
+      </c>
+      <c r="B199" t="s">
+        <v>733</v>
+      </c>
+    </row>
+    <row r="200" spans="1:3">
+      <c r="A200" t="s">
+        <v>24</v>
+      </c>
+      <c r="B200" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="201" spans="1:3">
+      <c r="A201" t="s">
+        <v>26</v>
+      </c>
+      <c r="B201" t="s">
+        <v>734</v>
+      </c>
+    </row>
+    <row r="202" spans="1:3">
+      <c r="A202" t="s">
+        <v>26</v>
+      </c>
+      <c r="B202" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="203" spans="1:3">
+      <c r="A203" t="s">
+        <v>26</v>
+      </c>
+      <c r="B203" t="s">
+        <v>736</v>
+      </c>
+    </row>
+    <row r="204" spans="1:3">
+      <c r="A204" t="s">
+        <v>26</v>
+      </c>
+      <c r="B204" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="205" spans="1:3">
+      <c r="A205" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="206" spans="1:3">
+      <c r="A206" t="s">
+        <v>31</v>
+      </c>
+      <c r="B206" t="s">
+        <v>32</v>
+      </c>
+      <c r="C206" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="207" spans="1:3">
+      <c r="A207" t="s">
+        <v>34</v>
+      </c>
+      <c r="B207">
+        <v>2</v>
+      </c>
+      <c r="C207">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="208" spans="1:3">
+      <c r="A208" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="209" spans="1:3">
+      <c r="A209" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="210" spans="1:3">
+      <c r="A210" t="s">
+        <v>738</v>
+      </c>
+      <c r="B210" t="s">
+        <v>646</v>
+      </c>
+    </row>
+    <row r="211" spans="1:3">
+      <c r="A211" t="s">
+        <v>19</v>
+      </c>
+      <c r="B211" t="s">
+        <v>713</v>
+      </c>
+      <c r="C211" t="s">
+        <v>739</v>
+      </c>
+    </row>
+    <row r="212" spans="1:3">
+      <c r="A212" t="s">
+        <v>22</v>
+      </c>
+      <c r="B212" t="s">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="213" spans="1:3">
+      <c r="A213" t="s">
+        <v>24</v>
+      </c>
+      <c r="B213" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="214" spans="1:3">
+      <c r="A214" t="s">
+        <v>26</v>
+      </c>
+      <c r="B214" t="s">
+        <v>741</v>
+      </c>
+    </row>
+    <row r="215" spans="1:3">
+      <c r="A215" t="s">
+        <v>26</v>
+      </c>
+      <c r="B215" t="s">
+        <v>718</v>
+      </c>
+    </row>
+    <row r="216" spans="1:3">
+      <c r="A216" t="s">
+        <v>26</v>
+      </c>
+      <c r="B216" t="s">
+        <v>716</v>
+      </c>
+    </row>
+    <row r="217" spans="1:3">
+      <c r="A217" t="s">
+        <v>26</v>
+      </c>
+      <c r="B217" t="s">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="218" spans="1:3">
+      <c r="A218" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="219" spans="1:3">
+      <c r="A219" t="s">
+        <v>31</v>
+      </c>
+      <c r="B219" t="s">
+        <v>32</v>
+      </c>
+      <c r="C219" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="220" spans="1:3">
+      <c r="A220" t="s">
+        <v>34</v>
+      </c>
+      <c r="B220">
+        <v>1</v>
+      </c>
+      <c r="C220">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="221" spans="1:3">
+      <c r="A221" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="222" spans="1:3">
+      <c r="A222" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="223" spans="1:3">
+      <c r="A223" t="s">
+        <v>742</v>
+      </c>
+      <c r="B223" t="s">
+        <v>646</v>
+      </c>
+    </row>
+    <row r="224" spans="1:3">
+      <c r="A224" t="s">
+        <v>19</v>
+      </c>
+      <c r="B224" t="s">
+        <v>713</v>
+      </c>
+      <c r="C224" t="s">
+        <v>743</v>
+      </c>
+    </row>
+    <row r="225" spans="1:3">
+      <c r="A225" t="s">
+        <v>22</v>
+      </c>
+      <c r="B225" t="s">
+        <v>744</v>
+      </c>
+    </row>
+    <row r="226" spans="1:3">
+      <c r="A226" t="s">
+        <v>24</v>
+      </c>
+      <c r="B226" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="227" spans="1:3">
+      <c r="A227" t="s">
+        <v>26</v>
+      </c>
+      <c r="B227" t="s">
+        <v>745</v>
+      </c>
+    </row>
+    <row r="228" spans="1:3">
+      <c r="A228" t="s">
+        <v>26</v>
+      </c>
+      <c r="B228" t="s">
+        <v>746</v>
+      </c>
+    </row>
+    <row r="229" spans="1:3">
+      <c r="A229" t="s">
+        <v>26</v>
+      </c>
+      <c r="B229" t="s">
+        <v>747</v>
+      </c>
+    </row>
+    <row r="230" spans="1:3">
+      <c r="A230" t="s">
+        <v>26</v>
+      </c>
+      <c r="B230" t="s">
+        <v>748</v>
+      </c>
+    </row>
+    <row r="231" spans="1:3">
+      <c r="A231" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="232" spans="1:3">
+      <c r="A232" t="s">
+        <v>31</v>
+      </c>
+      <c r="B232" t="s">
+        <v>32</v>
+      </c>
+      <c r="C232" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="233" spans="1:3">
+      <c r="A233" t="s">
+        <v>34</v>
+      </c>
+      <c r="B233">
+        <v>1</v>
+      </c>
+      <c r="C233">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="234" spans="1:3">
+      <c r="A234" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="235" spans="1:3">
+      <c r="A235" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="236" spans="1:3">
+      <c r="A236" t="s">
+        <v>749</v>
+      </c>
+      <c r="B236" t="s">
+        <v>646</v>
+      </c>
+    </row>
+    <row r="237" spans="1:3">
+      <c r="A237" t="s">
+        <v>19</v>
+      </c>
+      <c r="B237" t="s">
+        <v>750</v>
+      </c>
+      <c r="C237" t="s">
+        <v>751</v>
+      </c>
+    </row>
+    <row r="238" spans="1:3">
+      <c r="A238" t="s">
+        <v>22</v>
+      </c>
+      <c r="B238" t="s">
+        <v>752</v>
+      </c>
+    </row>
+    <row r="239" spans="1:3">
+      <c r="A239" t="s">
+        <v>24</v>
+      </c>
+      <c r="B239" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="240" spans="1:3">
+      <c r="A240" t="s">
+        <v>26</v>
+      </c>
+      <c r="B240" t="s">
+        <v>753</v>
+      </c>
+    </row>
+    <row r="241" spans="1:3">
+      <c r="A241" t="s">
+        <v>26</v>
+      </c>
+      <c r="B241" t="s">
+        <v>754</v>
+      </c>
+    </row>
+    <row r="242" spans="1:3">
+      <c r="A242" t="s">
+        <v>26</v>
+      </c>
+      <c r="B242" t="s">
+        <v>755</v>
+      </c>
+    </row>
+    <row r="243" spans="1:3">
+      <c r="A243" t="s">
+        <v>26</v>
+      </c>
+      <c r="B243" t="s">
+        <v>756</v>
+      </c>
+    </row>
+    <row r="244" spans="1:3">
+      <c r="A244" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="245" spans="1:3">
+      <c r="A245" t="s">
+        <v>31</v>
+      </c>
+      <c r="B245" t="s">
+        <v>32</v>
+      </c>
+      <c r="C245" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="246" spans="1:3">
+      <c r="A246" t="s">
+        <v>34</v>
+      </c>
+      <c r="B246">
+        <v>2</v>
+      </c>
+      <c r="C246">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="247" spans="1:3">
+      <c r="A247" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="248" spans="1:3">
+      <c r="A248" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="249" spans="1:3">
+      <c r="A249" t="s">
+        <v>757</v>
+      </c>
+      <c r="B249" t="s">
+        <v>646</v>
+      </c>
+    </row>
+    <row r="250" spans="1:3">
+      <c r="A250" t="s">
+        <v>19</v>
+      </c>
+      <c r="B250" t="s">
+        <v>750</v>
+      </c>
+      <c r="C250" t="s">
+        <v>758</v>
+      </c>
+    </row>
+    <row r="251" spans="1:3">
+      <c r="A251" t="s">
+        <v>22</v>
+      </c>
+      <c r="B251" t="s">
+        <v>759</v>
+      </c>
+    </row>
+    <row r="252" spans="1:3">
+      <c r="A252" t="s">
+        <v>24</v>
+      </c>
+      <c r="B252" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="253" spans="1:3">
+      <c r="A253" t="s">
+        <v>26</v>
+      </c>
+      <c r="B253" t="s">
+        <v>760</v>
+      </c>
+    </row>
+    <row r="254" spans="1:3">
+      <c r="A254" t="s">
+        <v>26</v>
+      </c>
+      <c r="B254" t="s">
+        <v>754</v>
+      </c>
+    </row>
+    <row r="255" spans="1:3">
+      <c r="A255" t="s">
+        <v>26</v>
+      </c>
+      <c r="B255" t="s">
+        <v>755</v>
+      </c>
+    </row>
+    <row r="256" spans="1:3">
+      <c r="A256" t="s">
+        <v>26</v>
+      </c>
+      <c r="B256" t="s">
+        <v>745</v>
+      </c>
+    </row>
+    <row r="257" spans="1:3">
+      <c r="A257" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="258" spans="1:3">
+      <c r="A258" t="s">
+        <v>31</v>
+      </c>
+      <c r="B258" t="s">
+        <v>32</v>
+      </c>
+      <c r="C258" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="259" spans="1:3">
+      <c r="A259" t="s">
+        <v>34</v>
+      </c>
+      <c r="B259">
+        <v>1</v>
+      </c>
+      <c r="C259">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="260" spans="1:3">
+      <c r="A260" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="261" spans="1:3">
+      <c r="A261" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="262" spans="1:3">
+      <c r="A262" t="s">
+        <v>761</v>
+      </c>
+      <c r="B262" t="s">
+        <v>646</v>
+      </c>
+    </row>
+    <row r="263" spans="1:3">
+      <c r="A263" t="s">
+        <v>19</v>
+      </c>
+      <c r="B263" t="s">
+        <v>762</v>
+      </c>
+      <c r="C263" t="s">
+        <v>763</v>
+      </c>
+    </row>
+    <row r="264" spans="1:3">
+      <c r="A264" t="s">
+        <v>22</v>
+      </c>
+      <c r="B264" t="s">
+        <v>764</v>
+      </c>
+    </row>
+    <row r="265" spans="1:3">
+      <c r="A265" t="s">
+        <v>24</v>
+      </c>
+      <c r="B265" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="266" spans="1:3">
+      <c r="A266" t="s">
+        <v>26</v>
+      </c>
+      <c r="B266" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="267" spans="1:3">
+      <c r="A267" t="s">
+        <v>26</v>
+      </c>
+      <c r="B267" t="s">
+        <v>766</v>
+      </c>
+    </row>
+    <row r="268" spans="1:3">
+      <c r="A268" t="s">
+        <v>26</v>
+      </c>
+      <c r="B268" t="s">
+        <v>767</v>
+      </c>
+    </row>
+    <row r="269" spans="1:3">
+      <c r="A269" t="s">
+        <v>26</v>
+      </c>
+      <c r="B269" t="s">
+        <v>768</v>
+      </c>
+    </row>
+    <row r="270" spans="1:3">
+      <c r="A270" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="271" spans="1:3">
+      <c r="A271" t="s">
+        <v>31</v>
+      </c>
+      <c r="B271" t="s">
+        <v>32</v>
+      </c>
+      <c r="C271" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="272" spans="1:3">
+      <c r="A272" t="s">
+        <v>34</v>
+      </c>
+      <c r="B272">
+        <v>2</v>
+      </c>
+      <c r="C272">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="273" spans="1:3">
+      <c r="A273" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="274" spans="1:3">
+      <c r="A274" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="275" spans="1:3">
+      <c r="A275" t="s">
+        <v>769</v>
+      </c>
+      <c r="B275" t="s">
+        <v>646</v>
+      </c>
+    </row>
+    <row r="276" spans="1:3">
+      <c r="A276" t="s">
+        <v>19</v>
+      </c>
+      <c r="B276" t="s">
+        <v>770</v>
+      </c>
+      <c r="C276" t="s">
+        <v>771</v>
+      </c>
+    </row>
+    <row r="277" spans="1:3">
+      <c r="A277" t="s">
+        <v>22</v>
+      </c>
+      <c r="B277" t="s">
+        <v>772</v>
+      </c>
+    </row>
+    <row r="278" spans="1:3">
+      <c r="A278" t="s">
+        <v>24</v>
+      </c>
+      <c r="B278" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="279" spans="1:3">
+      <c r="A279" t="s">
+        <v>26</v>
+      </c>
+      <c r="B279" t="s">
+        <v>773</v>
+      </c>
+    </row>
+    <row r="280" spans="1:3">
+      <c r="A280" t="s">
+        <v>26</v>
+      </c>
+      <c r="B280" t="s">
+        <v>774</v>
+      </c>
+    </row>
+    <row r="281" spans="1:3">
+      <c r="A281" t="s">
+        <v>26</v>
+      </c>
+      <c r="B281" t="s">
+        <v>775</v>
+      </c>
+    </row>
+    <row r="282" spans="1:3">
+      <c r="A282" t="s">
+        <v>26</v>
+      </c>
+      <c r="B282" t="s">
+        <v>776</v>
+      </c>
+    </row>
+    <row r="283" spans="1:3">
+      <c r="A283" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="284" spans="1:3">
+      <c r="A284" t="s">
+        <v>31</v>
+      </c>
+      <c r="B284" t="s">
+        <v>32</v>
+      </c>
+      <c r="C284" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="285" spans="1:3">
+      <c r="A285" t="s">
+        <v>34</v>
+      </c>
+      <c r="B285">
+        <v>2</v>
+      </c>
+      <c r="C285">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="286" spans="1:3">
+      <c r="A286" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="287" spans="1:3">
+      <c r="A287" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="288" spans="1:3">
+      <c r="A288" t="s">
+        <v>777</v>
+      </c>
+      <c r="B288" t="s">
+        <v>646</v>
+      </c>
+    </row>
+    <row r="289" spans="1:3">
+      <c r="A289" t="s">
+        <v>19</v>
+      </c>
+      <c r="B289" t="s">
+        <v>770</v>
+      </c>
+      <c r="C289" t="s">
+        <v>778</v>
+      </c>
+    </row>
+    <row r="290" spans="1:3">
+      <c r="A290" t="s">
+        <v>22</v>
+      </c>
+      <c r="B290" t="s">
+        <v>779</v>
+      </c>
+    </row>
+    <row r="291" spans="1:3">
+      <c r="A291" t="s">
+        <v>24</v>
+      </c>
+      <c r="B291" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="292" spans="1:3">
+      <c r="A292" t="s">
+        <v>26</v>
+      </c>
+      <c r="B292" t="s">
+        <v>780</v>
+      </c>
+    </row>
+    <row r="293" spans="1:3">
+      <c r="A293" t="s">
+        <v>26</v>
+      </c>
+      <c r="B293" t="s">
+        <v>745</v>
+      </c>
+    </row>
+    <row r="294" spans="1:3">
+      <c r="A294" t="s">
+        <v>26</v>
+      </c>
+      <c r="B294" t="s">
+        <v>781</v>
+      </c>
+    </row>
+    <row r="295" spans="1:3">
+      <c r="A295" t="s">
+        <v>26</v>
+      </c>
+      <c r="B295" t="s">
+        <v>782</v>
+      </c>
+    </row>
+    <row r="296" spans="1:3">
+      <c r="A296" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="297" spans="1:3">
+      <c r="A297" t="s">
+        <v>31</v>
+      </c>
+      <c r="B297" t="s">
+        <v>32</v>
+      </c>
+      <c r="C297" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="298" spans="1:3">
+      <c r="A298" t="s">
+        <v>34</v>
+      </c>
+      <c r="B298">
+        <v>1</v>
+      </c>
+      <c r="C298">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="299" spans="1:3">
+      <c r="A299" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="300" spans="1:3">
+      <c r="A300" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="301" spans="1:3">
+      <c r="A301" t="s">
+        <v>783</v>
+      </c>
+      <c r="B301" t="s">
+        <v>646</v>
+      </c>
+    </row>
+    <row r="302" spans="1:3">
+      <c r="A302" t="s">
+        <v>19</v>
+      </c>
+      <c r="B302" t="s">
+        <v>784</v>
+      </c>
+      <c r="C302" t="s">
+        <v>785</v>
+      </c>
+    </row>
+    <row r="303" spans="1:3">
+      <c r="A303" t="s">
+        <v>22</v>
+      </c>
+      <c r="B303" t="s">
+        <v>786</v>
+      </c>
+    </row>
+    <row r="304" spans="1:3">
+      <c r="A304" t="s">
+        <v>24</v>
+      </c>
+      <c r="B304" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="305" spans="1:3">
+      <c r="A305" t="s">
+        <v>26</v>
+      </c>
+      <c r="B305" t="s">
+        <v>787</v>
+      </c>
+    </row>
+    <row r="306" spans="1:3">
+      <c r="A306" t="s">
+        <v>26</v>
+      </c>
+      <c r="B306" t="s">
+        <v>788</v>
+      </c>
+    </row>
+    <row r="307" spans="1:3">
+      <c r="A307" t="s">
+        <v>26</v>
+      </c>
+      <c r="B307" t="s">
+        <v>789</v>
+      </c>
+    </row>
+    <row r="308" spans="1:3">
+      <c r="A308" t="s">
+        <v>26</v>
+      </c>
+      <c r="B308" t="s">
+        <v>790</v>
+      </c>
+    </row>
+    <row r="309" spans="1:3">
+      <c r="A309" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="310" spans="1:3">
+      <c r="A310" t="s">
+        <v>31</v>
+      </c>
+      <c r="B310" t="s">
+        <v>32</v>
+      </c>
+      <c r="C310" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="311" spans="1:3">
+      <c r="A311" t="s">
+        <v>34</v>
+      </c>
+      <c r="B311">
+        <v>2</v>
+      </c>
+      <c r="C311">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="312" spans="1:3">
+      <c r="A312" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="313" spans="1:3">
+      <c r="A313" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="314" spans="1:3">
+      <c r="A314" t="s">
+        <v>791</v>
+      </c>
+      <c r="B314" t="s">
+        <v>646</v>
+      </c>
+    </row>
+    <row r="315" spans="1:3">
+      <c r="A315" t="s">
+        <v>19</v>
+      </c>
+      <c r="B315" t="s">
+        <v>792</v>
+      </c>
+      <c r="C315" t="s">
+        <v>793</v>
+      </c>
+    </row>
+    <row r="316" spans="1:3">
+      <c r="A316" t="s">
+        <v>22</v>
+      </c>
+      <c r="B316" t="s">
+        <v>794</v>
+      </c>
+    </row>
+    <row r="317" spans="1:3">
+      <c r="A317" t="s">
+        <v>24</v>
+      </c>
+      <c r="B317" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="318" spans="1:3">
+      <c r="A318" t="s">
+        <v>26</v>
+      </c>
+      <c r="B318" t="s">
+        <v>776</v>
+      </c>
+    </row>
+    <row r="319" spans="1:3">
+      <c r="A319" t="s">
+        <v>26</v>
+      </c>
+      <c r="B319" t="s">
+        <v>795</v>
+      </c>
+    </row>
+    <row r="320" spans="1:3">
+      <c r="A320" t="s">
+        <v>26</v>
+      </c>
+      <c r="B320" t="s">
+        <v>796</v>
+      </c>
+    </row>
+    <row r="321" spans="1:3">
+      <c r="A321" t="s">
+        <v>26</v>
+      </c>
+      <c r="B321" t="s">
+        <v>797</v>
+      </c>
+    </row>
+    <row r="322" spans="1:3">
+      <c r="A322" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="323" spans="1:3">
+      <c r="A323" t="s">
+        <v>31</v>
+      </c>
+      <c r="B323" t="s">
+        <v>32</v>
+      </c>
+      <c r="C323" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="324" spans="1:3">
+      <c r="A324" t="s">
+        <v>34</v>
+      </c>
+      <c r="B324">
+        <v>2</v>
+      </c>
+      <c r="C324">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="325" spans="1:3">
+      <c r="A325" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="326" spans="1:3">
+      <c r="A326" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="327" spans="1:3">
+      <c r="A327" t="s">
+        <v>798</v>
+      </c>
+      <c r="B327" t="s">
+        <v>646</v>
+      </c>
+    </row>
+    <row r="328" spans="1:3">
+      <c r="A328" t="s">
+        <v>19</v>
+      </c>
+      <c r="B328" t="s">
+        <v>799</v>
+      </c>
+      <c r="C328" t="s">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="329" spans="1:3">
+      <c r="A329" t="s">
+        <v>22</v>
+      </c>
+      <c r="B329" t="s">
+        <v>801</v>
+      </c>
+    </row>
+    <row r="330" spans="1:3">
+      <c r="A330" t="s">
+        <v>24</v>
+      </c>
+      <c r="B330" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="331" spans="1:3">
+      <c r="A331" t="s">
+        <v>26</v>
+      </c>
+      <c r="B331" t="s">
+        <v>802</v>
+      </c>
+    </row>
+    <row r="332" spans="1:3">
+      <c r="A332" t="s">
+        <v>26</v>
+      </c>
+      <c r="B332" t="s">
+        <v>803</v>
+      </c>
+    </row>
+    <row r="333" spans="1:3">
+      <c r="A333" t="s">
+        <v>26</v>
+      </c>
+      <c r="B333" t="s">
+        <v>804</v>
+      </c>
+    </row>
+    <row r="334" spans="1:3">
+      <c r="A334" t="s">
+        <v>26</v>
+      </c>
+      <c r="B334" t="s">
+        <v>805</v>
+      </c>
+    </row>
+    <row r="335" spans="1:3">
+      <c r="A335" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="336" spans="1:3">
+      <c r="A336" t="s">
+        <v>31</v>
+      </c>
+      <c r="B336" t="s">
+        <v>32</v>
+      </c>
+      <c r="C336" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="337" spans="1:3">
+      <c r="A337" t="s">
+        <v>34</v>
+      </c>
+      <c r="B337">
+        <v>3</v>
+      </c>
+      <c r="C337">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="338" spans="1:3">
+      <c r="A338" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="339" spans="1:3">
+      <c r="A339" t="s">
+        <v>36</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>